--- a/assincrono/Resultados-teste-usabilidade.xlsx
+++ b/assincrono/Resultados-teste-usabilidade.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Minutos e segundos em colunas separadas. Na tarefa 9 (emergência), anote o tempo até tocar em ligar. Limite de 10 minutos por tarefa: passou disso, marque Não conseguiu.</t>
+          <t>Minutos e segundos em colunas separadas. Nas tarefas 9 e C6 (emergência), a tela final também mostra em quantos segundos a pessoa ligou para o 192: anote em Observações. Limite de 10 minutos por tarefa: passou disso, marque Não conseguiu.</t>
         </is>
       </c>
     </row>

--- a/assincrono/Resultados-teste-usabilidade.xlsx
+++ b/assincrono/Resultados-teste-usabilidade.xlsx
@@ -793,7 +793,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>As respostas do teste sem condutor entram sozinhas: importe esta planilha para a planilha de respostas do Formulário Google e use o menu Cantinho → Atualizar resultados (veja o LEIA-ME). Os IDs ficam FA1, FA2… (família) e CUA1, CUA2… (cuidadoras), e "Quem conduziu" mostra Assíncrono.</t>
+          <t>As respostas do teste sem condutor entram sozinhas: importe esta planilha para a planilha de respostas do Formulário Google e use o menu Cantinho → Atualizar resultados (veja o LEIA-ME). Os IDs ficam FA1, FA2… (família) e CUA1, CUA2… (cuidadoras), e "Quem conduziu" mostra Assíncrono. Quem pediu dica no teste aparece com Resultado "Com dica", e o nível e o momento da dica ficam em Observações.</t>
         </is>
       </c>
     </row>

--- a/assincrono/Resultados-teste-usabilidade.xlsx
+++ b/assincrono/Resultados-teste-usabilidade.xlsx
@@ -293,6 +293,38 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FECACA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FDE68A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00DCFCE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -805,7 +837,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Calcula sozinho: quantas pessoas fizeram cada tarefa, % que conseguiu sozinha, tempo médio, facilidade média e a nota de recomendação (NPS).</t>
+          <t>Calcula sozinho: quantas pessoas fizeram cada tarefa, % que conseguiu sozinha, tempo médio, facilidade média, menor nota, um alerta por tarefa (Revisar, Atenção ou OK) e a nota de recomendação (NPS).</t>
         </is>
       </c>
     </row>
@@ -945,7 +977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -956,6 +988,8 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1020,6 +1054,16 @@
           <t>Facilidade média</t>
         </is>
       </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>Menor nota</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>Alerta</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -1054,6 +1098,14 @@
         <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A6,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",AVERAGEIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A6,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
         <v/>
       </c>
+      <c r="I6" s="9">
+        <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A6,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",_xlfn.MINIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A6,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="J6" s="9">
+        <f>IF(C6=0,"-",IF(OR(AND(ISNUMBER(H6),H6&lt;3),D6&lt;0.7),"Revisar",IF(AND(ISNUMBER(H6),H6&gt;=4,E6+F6&gt;0),"Atenção","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -1088,6 +1140,14 @@
         <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A7,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",AVERAGEIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A7,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
         <v/>
       </c>
+      <c r="I7" s="9">
+        <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A7,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",_xlfn.MINIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A7,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="J7" s="9">
+        <f>IF(C7=0,"-",IF(OR(AND(ISNUMBER(H7),H7&lt;3),D7&lt;0.7),"Revisar",IF(AND(ISNUMBER(H7),H7&gt;=4,E7+F7&gt;0),"Atenção","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
@@ -1122,6 +1182,14 @@
         <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A8,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",AVERAGEIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A8,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
         <v/>
       </c>
+      <c r="I8" s="9">
+        <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A8,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",_xlfn.MINIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A8,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="J8" s="9">
+        <f>IF(C8=0,"-",IF(OR(AND(ISNUMBER(H8),H8&lt;3),D8&lt;0.7),"Revisar",IF(AND(ISNUMBER(H8),H8&gt;=4,E8+F8&gt;0),"Atenção","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
@@ -1156,6 +1224,14 @@
         <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A9,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",AVERAGEIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A9,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
         <v/>
       </c>
+      <c r="I9" s="9">
+        <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A9,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",_xlfn.MINIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A9,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="J9" s="9">
+        <f>IF(C9=0,"-",IF(OR(AND(ISNUMBER(H9),H9&lt;3),D9&lt;0.7),"Revisar",IF(AND(ISNUMBER(H9),H9&gt;=4,E9+F9&gt;0),"Atenção","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
@@ -1190,6 +1266,14 @@
         <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A10,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",AVERAGEIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A10,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
         <v/>
       </c>
+      <c r="I10" s="9">
+        <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A10,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",_xlfn.MINIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A10,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="J10" s="9">
+        <f>IF(C10=0,"-",IF(OR(AND(ISNUMBER(H10),H10&lt;3),D10&lt;0.7),"Revisar",IF(AND(ISNUMBER(H10),H10&gt;=4,E10+F10&gt;0),"Atenção","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -1224,6 +1308,14 @@
         <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A11,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",AVERAGEIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A11,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
         <v/>
       </c>
+      <c r="I11" s="9">
+        <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A11,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",_xlfn.MINIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A11,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="J11" s="9">
+        <f>IF(C11=0,"-",IF(OR(AND(ISNUMBER(H11),H11&lt;3),D11&lt;0.7),"Revisar",IF(AND(ISNUMBER(H11),H11&gt;=4,E11+F11&gt;0),"Atenção","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
@@ -1258,6 +1350,14 @@
         <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A12,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",AVERAGEIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A12,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
         <v/>
       </c>
+      <c r="I12" s="9">
+        <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A12,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",_xlfn.MINIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A12,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="J12" s="9">
+        <f>IF(C12=0,"-",IF(OR(AND(ISNUMBER(H12),H12&lt;3),D12&lt;0.7),"Revisar",IF(AND(ISNUMBER(H12),H12&gt;=4,E12+F12&gt;0),"Atenção","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
@@ -1292,6 +1392,14 @@
         <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A13,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",AVERAGEIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A13,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
         <v/>
       </c>
+      <c r="I13" s="9">
+        <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A13,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",_xlfn.MINIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A13,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="J13" s="9">
+        <f>IF(C13=0,"-",IF(OR(AND(ISNUMBER(H13),H13&lt;3),D13&lt;0.7),"Revisar",IF(AND(ISNUMBER(H13),H13&gt;=4,E13+F13&gt;0),"Atenção","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
@@ -1326,6 +1434,14 @@
         <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A14,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",AVERAGEIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A14,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
         <v/>
       </c>
+      <c r="I14" s="9">
+        <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A14,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",_xlfn.MINIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A14,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="J14" s="9">
+        <f>IF(C14=0,"-",IF(OR(AND(ISNUMBER(H14),H14&lt;3),D14&lt;0.7),"Revisar",IF(AND(ISNUMBER(H14),H14&gt;=4,E14+F14&gt;0),"Atenção","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
@@ -1360,6 +1476,14 @@
         <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A15,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",AVERAGEIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A15,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
         <v/>
       </c>
+      <c r="I15" s="9">
+        <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A15,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",_xlfn.MINIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A15,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="J15" s="9">
+        <f>IF(C15=0,"-",IF(OR(AND(ISNUMBER(H15),H15&lt;3),D15&lt;0.7),"Revisar",IF(AND(ISNUMBER(H15),H15&gt;=4,E15+F15&gt;0),"Atenção","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
@@ -1394,6 +1518,14 @@
         <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A16,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",AVERAGEIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A16,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
         <v/>
       </c>
+      <c r="I16" s="9">
+        <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A16,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",_xlfn.MINIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A16,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="J16" s="9">
+        <f>IF(C16=0,"-",IF(OR(AND(ISNUMBER(H16),H16&lt;3),D16&lt;0.7),"Revisar",IF(AND(ISNUMBER(H16),H16&gt;=4,E16+F16&gt;0),"Atenção","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
@@ -1428,6 +1560,14 @@
         <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A17,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",AVERAGEIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A17,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
         <v/>
       </c>
+      <c r="I17" s="9">
+        <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A17,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",_xlfn.MINIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A17,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="J17" s="9">
+        <f>IF(C17=0,"-",IF(OR(AND(ISNUMBER(H17),H17&lt;3),D17&lt;0.7),"Revisar",IF(AND(ISNUMBER(H17),H17&gt;=4,E17+F17&gt;0),"Atenção","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
@@ -1460,6 +1600,14 @@
       </c>
       <c r="H18" s="12">
         <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A18,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",AVERAGEIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A18,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="I18" s="9">
+        <f>IF(COUNTIFS('Tarefas família'!$B$5:$B$804,A18,'Tarefas família'!$H$5:$H$804,"&gt;0")=0,"-",_xlfn.MINIFS('Tarefas família'!$H$5:$H$804,'Tarefas família'!$B$5:$B$804,A18,'Tarefas família'!$H$5:$H$804,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="J18" s="9">
+        <f>IF(C18=0,"-",IF(OR(AND(ISNUMBER(H18),H18&lt;3),D18&lt;0.7),"Revisar",IF(AND(ISNUMBER(H18),H18&gt;=4,E18+F18&gt;0),"Atenção","OK")))</f>
         <v/>
       </c>
     </row>
@@ -1511,6 +1659,16 @@
           <t>Facilidade média</t>
         </is>
       </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>Menor nota</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>Alerta</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
@@ -1547,6 +1705,14 @@
         <f>IF(COUNTIFS('Tarefas cuidadoras'!$B$5:$B$804,A23,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0")=0,"-",AVERAGEIFS('Tarefas cuidadoras'!$H$5:$H$804,'Tarefas cuidadoras'!$B$5:$B$804,A23,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0"))</f>
         <v/>
       </c>
+      <c r="I23" s="9">
+        <f>IF(COUNTIFS('Tarefas cuidadoras'!$B$5:$B$804,A23,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0")=0,"-",_xlfn.MINIFS('Tarefas cuidadoras'!$H$5:$H$804,'Tarefas cuidadoras'!$B$5:$B$804,A23,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="J23" s="9">
+        <f>IF(C23=0,"-",IF(OR(AND(ISNUMBER(H23),H23&lt;3),D23&lt;0.7),"Revisar",IF(AND(ISNUMBER(H23),H23&gt;=4,E23+F23&gt;0),"Atenção","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
@@ -1583,6 +1749,14 @@
         <f>IF(COUNTIFS('Tarefas cuidadoras'!$B$5:$B$804,A24,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0")=0,"-",AVERAGEIFS('Tarefas cuidadoras'!$H$5:$H$804,'Tarefas cuidadoras'!$B$5:$B$804,A24,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0"))</f>
         <v/>
       </c>
+      <c r="I24" s="9">
+        <f>IF(COUNTIFS('Tarefas cuidadoras'!$B$5:$B$804,A24,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0")=0,"-",_xlfn.MINIFS('Tarefas cuidadoras'!$H$5:$H$804,'Tarefas cuidadoras'!$B$5:$B$804,A24,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="J24" s="9">
+        <f>IF(C24=0,"-",IF(OR(AND(ISNUMBER(H24),H24&lt;3),D24&lt;0.7),"Revisar",IF(AND(ISNUMBER(H24),H24&gt;=4,E24+F24&gt;0),"Atenção","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
@@ -1619,6 +1793,14 @@
         <f>IF(COUNTIFS('Tarefas cuidadoras'!$B$5:$B$804,A25,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0")=0,"-",AVERAGEIFS('Tarefas cuidadoras'!$H$5:$H$804,'Tarefas cuidadoras'!$B$5:$B$804,A25,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0"))</f>
         <v/>
       </c>
+      <c r="I25" s="9">
+        <f>IF(COUNTIFS('Tarefas cuidadoras'!$B$5:$B$804,A25,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0")=0,"-",_xlfn.MINIFS('Tarefas cuidadoras'!$H$5:$H$804,'Tarefas cuidadoras'!$B$5:$B$804,A25,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="J25" s="9">
+        <f>IF(C25=0,"-",IF(OR(AND(ISNUMBER(H25),H25&lt;3),D25&lt;0.7),"Revisar",IF(AND(ISNUMBER(H25),H25&gt;=4,E25+F25&gt;0),"Atenção","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
@@ -1655,6 +1837,14 @@
         <f>IF(COUNTIFS('Tarefas cuidadoras'!$B$5:$B$804,A26,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0")=0,"-",AVERAGEIFS('Tarefas cuidadoras'!$H$5:$H$804,'Tarefas cuidadoras'!$B$5:$B$804,A26,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0"))</f>
         <v/>
       </c>
+      <c r="I26" s="9">
+        <f>IF(COUNTIFS('Tarefas cuidadoras'!$B$5:$B$804,A26,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0")=0,"-",_xlfn.MINIFS('Tarefas cuidadoras'!$H$5:$H$804,'Tarefas cuidadoras'!$B$5:$B$804,A26,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="J26" s="9">
+        <f>IF(C26=0,"-",IF(OR(AND(ISNUMBER(H26),H26&lt;3),D26&lt;0.7),"Revisar",IF(AND(ISNUMBER(H26),H26&gt;=4,E26+F26&gt;0),"Atenção","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
@@ -1691,6 +1881,14 @@
         <f>IF(COUNTIFS('Tarefas cuidadoras'!$B$5:$B$804,A27,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0")=0,"-",AVERAGEIFS('Tarefas cuidadoras'!$H$5:$H$804,'Tarefas cuidadoras'!$B$5:$B$804,A27,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0"))</f>
         <v/>
       </c>
+      <c r="I27" s="9">
+        <f>IF(COUNTIFS('Tarefas cuidadoras'!$B$5:$B$804,A27,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0")=0,"-",_xlfn.MINIFS('Tarefas cuidadoras'!$H$5:$H$804,'Tarefas cuidadoras'!$B$5:$B$804,A27,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="J27" s="9">
+        <f>IF(C27=0,"-",IF(OR(AND(ISNUMBER(H27),H27&lt;3),D27&lt;0.7),"Revisar",IF(AND(ISNUMBER(H27),H27&gt;=4,E27+F27&gt;0),"Atenção","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
@@ -1727,6 +1925,14 @@
         <f>IF(COUNTIFS('Tarefas cuidadoras'!$B$5:$B$804,A28,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0")=0,"-",AVERAGEIFS('Tarefas cuidadoras'!$H$5:$H$804,'Tarefas cuidadoras'!$B$5:$B$804,A28,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0"))</f>
         <v/>
       </c>
+      <c r="I28" s="9">
+        <f>IF(COUNTIFS('Tarefas cuidadoras'!$B$5:$B$804,A28,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0")=0,"-",_xlfn.MINIFS('Tarefas cuidadoras'!$H$5:$H$804,'Tarefas cuidadoras'!$B$5:$B$804,A28,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="J28" s="9">
+        <f>IF(C28=0,"-",IF(OR(AND(ISNUMBER(H28),H28&lt;3),D28&lt;0.7),"Revisar",IF(AND(ISNUMBER(H28),H28&gt;=4,E28+F28&gt;0),"Atenção","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
@@ -1763,6 +1969,14 @@
         <f>IF(COUNTIFS('Tarefas cuidadoras'!$B$5:$B$804,A29,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0")=0,"-",AVERAGEIFS('Tarefas cuidadoras'!$H$5:$H$804,'Tarefas cuidadoras'!$B$5:$B$804,A29,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0"))</f>
         <v/>
       </c>
+      <c r="I29" s="9">
+        <f>IF(COUNTIFS('Tarefas cuidadoras'!$B$5:$B$804,A29,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0")=0,"-",_xlfn.MINIFS('Tarefas cuidadoras'!$H$5:$H$804,'Tarefas cuidadoras'!$B$5:$B$804,A29,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="J29" s="9">
+        <f>IF(C29=0,"-",IF(OR(AND(ISNUMBER(H29),H29&lt;3),D29&lt;0.7),"Revisar",IF(AND(ISNUMBER(H29),H29&gt;=4,E29+F29&gt;0),"Atenção","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
@@ -1799,6 +2013,14 @@
         <f>IF(COUNTIFS('Tarefas cuidadoras'!$B$5:$B$804,A30,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0")=0,"-",AVERAGEIFS('Tarefas cuidadoras'!$H$5:$H$804,'Tarefas cuidadoras'!$B$5:$B$804,A30,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0"))</f>
         <v/>
       </c>
+      <c r="I30" s="9">
+        <f>IF(COUNTIFS('Tarefas cuidadoras'!$B$5:$B$804,A30,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0")=0,"-",_xlfn.MINIFS('Tarefas cuidadoras'!$H$5:$H$804,'Tarefas cuidadoras'!$B$5:$B$804,A30,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="J30" s="9">
+        <f>IF(C30=0,"-",IF(OR(AND(ISNUMBER(H30),H30&lt;3),D30&lt;0.7),"Revisar",IF(AND(ISNUMBER(H30),H30&gt;=4,E30+F30&gt;0),"Atenção","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
@@ -1835,6 +2057,14 @@
         <f>IF(COUNTIFS('Tarefas cuidadoras'!$B$5:$B$804,A31,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0")=0,"-",AVERAGEIFS('Tarefas cuidadoras'!$H$5:$H$804,'Tarefas cuidadoras'!$B$5:$B$804,A31,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0"))</f>
         <v/>
       </c>
+      <c r="I31" s="9">
+        <f>IF(COUNTIFS('Tarefas cuidadoras'!$B$5:$B$804,A31,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0")=0,"-",_xlfn.MINIFS('Tarefas cuidadoras'!$H$5:$H$804,'Tarefas cuidadoras'!$B$5:$B$804,A31,'Tarefas cuidadoras'!$H$5:$H$804,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="J31" s="9">
+        <f>IF(C31=0,"-",IF(OR(AND(ISNUMBER(H31),H31&lt;3),D31&lt;0.7),"Revisar",IF(AND(ISNUMBER(H31),H31&gt;=4,E31+F31&gt;0),"Atenção","OK")))</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -2047,7 +2277,50 @@
         <v/>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Alerta por tarefa: "Revisar" = facilidade média abaixo de 3 ou menos de 70% conseguiu sozinha. Comece por essas, principalmente as do dia a dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>"Atenção" = a nota foi 4 ou mais, mas alguém não conseguiu ou precisou de dica: a pessoa achou fácil e errou sem perceber. Leia os comentários e o caminho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>"OK" = sem sinal de problema. Com poucas pessoas, confira também a Menor nota: uma nota 1 ou 2 merece ler o comentário daquela pessoa.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="J6:J18">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$J6="Revisar"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>$J6="Atenção"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>$J6="OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J23:J31">
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>$J23="Revisar"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="1">
+      <formula>$J23="Atenção"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="2">
+      <formula>$J23="OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
